--- a/Permeability Measurements.xlsx
+++ b/Permeability Measurements.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universityofbergen-my.sharepoint.com/personal/qih018_uib_no/Documents/Master/MRI-Tools-master/Github organized codes/Excel Sheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="418" documentId="8_{210BB275-64F8-4429-93AD-05E0C984568A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6C4C5CA-0DDB-4CD3-A79D-C387F63837B0}"/>
+  <xr:revisionPtr revIDLastSave="445" documentId="8_{210BB275-64F8-4429-93AD-05E0C984568A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D6AF7C5-2FD7-4105-9518-CDF2014397D6}"/>
   <bookViews>
-    <workbookView xWindow="-135" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="1" xr2:uid="{792FBB64-665B-4D66-AD36-58F1170FDE40}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{792FBB64-665B-4D66-AD36-58F1170FDE40}"/>
   </bookViews>
   <sheets>
     <sheet name="Permeability" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="68">
   <si>
     <t>Brine</t>
   </si>
@@ -142,9 +142,6 @@
     <t>K=Q*μ*L/A*ΔP</t>
   </si>
   <si>
-    <t xml:space="preserve">  Date  ,   Time  , Cum. Min , Cyl4A Prs, O Press 2, O Press 3, Cyl4ARate, O Rate 2 , O Rate 3 ,  Cyl4A Vol  ,     C Vol 2     ,     C Vol 3     </t>
-  </si>
-  <si>
     <t>Pressure (bar)</t>
   </si>
   <si>
@@ -250,9 +247,6 @@
     <t>Q co2 (ml/h)</t>
   </si>
   <si>
-    <t>|</t>
-  </si>
-  <si>
     <t>ΔP(Q=1 ml/h) (Pa)</t>
   </si>
   <si>
@@ -263,6 +257,12 @@
   </si>
   <si>
     <t>Uncertainty Brine</t>
+  </si>
+  <si>
+    <t>*reported systematic uncertainties of the P and ΔP transducers</t>
+  </si>
+  <si>
+    <t>Endpoint relative permeabilty</t>
   </si>
 </sst>
 </file>
@@ -271,11 +271,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="183" formatCode="0.000E+00"/>
-    <numFmt numFmtId="185" formatCode="0.0"/>
-    <numFmt numFmtId="187" formatCode="0E+00"/>
+    <numFmt numFmtId="165" formatCode="0.000E+00"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0E+00"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -315,8 +315,16 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -335,8 +343,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -406,20 +420,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="21" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -439,17 +459,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="185" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -850,11 +878,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2651F5DE-55AB-4410-8C55-FFD7831DBEB7}">
-  <dimension ref="A1:Q39"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="12" bestFit="1" customWidth="1"/>
@@ -890,10 +918,10 @@
       </c>
       <c r="C3" s="1"/>
       <c r="E3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G3" t="s">
         <v>25</v>
@@ -902,19 +930,19 @@
         <v>25</v>
       </c>
       <c r="I3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L3" t="s">
+        <v>38</v>
+      </c>
+      <c r="M3" s="13" t="s">
         <v>39</v>
-      </c>
-      <c r="M3" s="16" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -937,7 +965,7 @@
         <f>(G4-$G$4)*100000</f>
         <v>0</v>
       </c>
-      <c r="M4" s="16"/>
+      <c r="M4" s="13"/>
     </row>
     <row r="5" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -978,7 +1006,7 @@
         <f>(F5*$B$22*$B$5/100)/($B$6/10000*J5)</f>
         <v>2.8050809132658365E-13</v>
       </c>
-      <c r="M5" s="16">
+      <c r="M5" s="13">
         <f>L5*1.01325*10^12</f>
         <v>0.2842248235366609</v>
       </c>
@@ -1022,15 +1050,15 @@
         <f>(F6*$B$22*$B$5/100)/($B$6/10000*J6)</f>
         <v>2.8019900578331175E-13</v>
       </c>
-      <c r="M6" s="16">
+      <c r="M6" s="13">
         <f t="shared" ref="M6:M8" si="2">L6*1.01325*10^12</f>
         <v>0.28391164260994062</v>
       </c>
-      <c r="O6" s="7" t="s">
+      <c r="O6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="P6" s="8"/>
-      <c r="Q6" s="9"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="6"/>
     </row>
     <row r="7" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
@@ -1071,15 +1099,15 @@
         <f>(F7*$B$22*$B$5/100)/($B$6/10000*J7)</f>
         <v>2.796632032379025E-13</v>
       </c>
-      <c r="M7" s="16">
+      <c r="M7" s="13">
         <f t="shared" si="2"/>
         <v>0.2833687406808047</v>
       </c>
-      <c r="O7" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="P7" s="11"/>
-      <c r="Q7" s="12"/>
+      <c r="O7" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="9"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -1120,7 +1148,7 @@
         <f>(F8*$B$22*$B$5/100)/($B$6/10000*J8)</f>
         <v>2.7953004029747388E-13</v>
       </c>
-      <c r="M8" s="16">
+      <c r="M8" s="13">
         <f t="shared" si="2"/>
         <v>0.2832338133314154</v>
       </c>
@@ -1135,11 +1163,11 @@
       <c r="C9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M9" s="14">
+      <c r="M9" s="11">
         <f>AVERAGE(M5:M8)</f>
         <v>0.28368475503970542</v>
       </c>
-      <c r="N9" s="14">
+      <c r="N9" s="11">
         <f>_xlfn.STDEV.P(M5:M8)</f>
         <v>4.0198428148310097E-4</v>
       </c>
@@ -1217,63 +1245,63 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="H20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="15">
+        <v>41</v>
+      </c>
+      <c r="B22" s="12">
         <v>1.0432E-3</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>35</v>
+      <c r="C22" s="3" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B23">
         <v>74</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>37</v>
+      <c r="C23" s="3" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B24">
         <f>273.15+20.55</f>
         <v>293.7</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>36</v>
+      <c r="C24" s="3" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25">
         <f>273.15+21.27</f>
         <v>294.41999999999996</v>
       </c>
-      <c r="C25" s="6" t="s">
-        <v>36</v>
+      <c r="C25" s="3" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B26">
         <f>(B25+B24)/2-273.15</f>
@@ -1282,106 +1310,22 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B27">
         <v>1001</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A37" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="5">
-        <v>74.099999999999994</v>
-      </c>
-      <c r="G37" s="5">
-        <v>0</v>
-      </c>
-      <c r="H37" s="5">
-        <v>0.75</v>
-      </c>
-      <c r="I37" s="13"/>
-      <c r="J37" s="13"/>
-      <c r="K37" s="13"/>
-      <c r="L37" s="13"/>
-      <c r="M37" s="13"/>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A38" s="3">
-        <v>45989</v>
-      </c>
-      <c r="B38" s="4">
-        <v>0.67847222222222225</v>
-      </c>
-      <c r="C38" s="5">
-        <v>10224.513000000001</v>
-      </c>
-      <c r="D38" s="5">
-        <v>0.08</v>
-      </c>
-      <c r="E38" s="5">
-        <v>10.88</v>
-      </c>
-      <c r="F38" s="5">
-        <v>74</v>
-      </c>
-      <c r="G38" s="5">
-        <v>0</v>
-      </c>
-      <c r="H38" s="5">
-        <v>3.72</v>
-      </c>
-      <c r="I38" s="5">
-        <v>0</v>
-      </c>
-      <c r="J38" s="5">
-        <v>472.86</v>
-      </c>
-      <c r="K38" s="5">
-        <v>0.77</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A39" s="3">
-        <v>45989</v>
-      </c>
-      <c r="B39" s="4">
-        <v>0.70834490740740741</v>
-      </c>
-      <c r="C39" s="5">
-        <v>10267.513000000001</v>
-      </c>
-      <c r="D39" s="5">
-        <v>0.08</v>
-      </c>
-      <c r="E39" s="5">
-        <v>41.85</v>
-      </c>
-      <c r="I39" s="5">
-        <v>0</v>
-      </c>
-      <c r="J39" s="5">
-        <v>472.86</v>
-      </c>
-      <c r="K39" s="5">
-        <v>0.09</v>
-      </c>
-      <c r="L39" s="5">
-        <v>-743.33</v>
-      </c>
+      <c r="C27" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="10"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1401,10 +1345,14 @@
   <dimension ref="A2:L25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="38" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.85546875" customWidth="1"/>
@@ -1413,283 +1361,301 @@
     <col min="17" max="17" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C3" t="s">
+    <row r="2" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="J3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
+    </row>
+    <row r="4" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4">
+        <v>7.3750000000000004E-5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>49</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K4" s="8"/>
+      <c r="L4" s="9"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6">
+        <f>B19/(1.01325*10^12)</f>
+        <v>2.7999013076733287E-13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D3" t="s">
+      <c r="B7" s="2">
+        <v>10.62</v>
+      </c>
+      <c r="C7">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="16">
+        <v>7.89</v>
+      </c>
+      <c r="C8">
+        <f>SQRT(PI()*(0.01/2*B8))</f>
+        <v>0.35204521042632769</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10">
+        <f>B9/(10^6*60*60)</f>
+        <v>2.7777777777777777E-10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11">
+        <f>$B$10*B4*($B$7/100)/($B$6*$B$8/10000)</f>
+        <v>9.8483690364024525</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12">
+        <f>B11/100000</f>
+        <v>9.8483690364024531E-5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B13">
+        <f>20/B12</f>
+        <v>203079.31116385007</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="E3" t="s">
-        <v>52</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" s="8"/>
-      <c r="L3" s="9"/>
-    </row>
-    <row r="4" spans="3:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D4">
+      <c r="B18" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="15">
+        <v>0.28370000000000001</v>
+      </c>
+      <c r="C19" s="15">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="D19" s="15">
+        <v>0.28370000000000001</v>
+      </c>
+      <c r="E19" s="15">
+        <v>4.0000000000000002E-4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" s="15">
+        <v>1</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" s="15">
+        <v>1</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="15">
         <v>7.3750000000000004E-5</v>
       </c>
-      <c r="E4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="K4" s="11"/>
-      <c r="L4" s="12"/>
-    </row>
-    <row r="5" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6">
-        <f>D19/(1.01325*10^12)</f>
-        <v>2.7999013076733287E-13</v>
-      </c>
-      <c r="E6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D7" s="2">
-        <v>10.62</v>
-      </c>
-      <c r="E7">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="8" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C8" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="19">
-        <v>7.89</v>
-      </c>
-      <c r="E8">
-        <f>SQRT(PI()*(0.01/2*D8))</f>
-        <v>0.35204521042632769</v>
-      </c>
-    </row>
-    <row r="9" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10">
-        <f>D9/(10^6*60*60)</f>
-        <v>2.7777777777777777E-10</v>
-      </c>
-    </row>
-    <row r="11" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11">
-        <f>$D$10*D4*($D$7/100)/($D$6*$D$8/10000)</f>
-        <v>9.8483690364024525</v>
-      </c>
-    </row>
-    <row r="12" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C12" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12">
-        <f>D11/100000</f>
-        <v>9.8483690364024531E-5</v>
-      </c>
-    </row>
-    <row r="13" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="D13">
-        <f>20/D12</f>
-        <v>203079.31116385007</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D18" t="s">
-        <v>56</v>
-      </c>
-      <c r="E18" t="s">
-        <v>65</v>
-      </c>
-      <c r="F18" t="s">
-        <v>0</v>
-      </c>
-      <c r="G18" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C19" t="s">
-        <v>57</v>
-      </c>
-      <c r="D19" s="18">
-        <v>0.28370000000000001</v>
-      </c>
-      <c r="E19" s="18">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F19" s="18">
-        <v>0.28370000000000001</v>
-      </c>
-      <c r="G19" s="18">
-        <v>4.0000000000000002E-4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C20" t="s">
-        <v>62</v>
-      </c>
-      <c r="D20" s="18">
-        <v>1</v>
-      </c>
-      <c r="E20" s="17" t="s">
+      <c r="C21" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" s="15">
+        <v>7.2810000000000003E-5</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" s="15">
+        <v>24.11</v>
+      </c>
+      <c r="C22" s="15">
+        <f>0.0025*B22</f>
+        <v>6.0275000000000002E-2</v>
+      </c>
+      <c r="D22" s="15">
+        <v>13.686999999999999</v>
+      </c>
+      <c r="E22" s="15">
+        <f>0.004*D22</f>
+        <v>5.4747999999999998E-2</v>
+      </c>
+      <c r="F22" t="s">
         <v>66</v>
       </c>
-      <c r="F20" s="18">
-        <v>1</v>
-      </c>
-      <c r="G20" s="17" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C21" t="s">
-        <v>61</v>
-      </c>
-      <c r="D21" s="18">
-        <v>7.3750000000000004E-5</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="F21" s="18">
-        <v>7.2810000000000003E-5</v>
-      </c>
-      <c r="G21" s="17" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C22" t="s">
-        <v>60</v>
-      </c>
-      <c r="D22" s="18">
-        <v>24.11</v>
-      </c>
-      <c r="E22" s="18">
-        <f>0.0025*D22</f>
-        <v>6.0275000000000002E-2</v>
-      </c>
-      <c r="F22" s="18">
-        <v>13.686999999999999</v>
-      </c>
-      <c r="G22" s="18">
-        <f>0.004*F22</f>
-        <v>5.4747999999999998E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C23" t="s">
-        <v>59</v>
-      </c>
-      <c r="D23" s="20">
-        <f>(D10*$D$21*$D$7/100)/($D$8/10000*D25)</f>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" s="17">
+        <f>(B10*$B$21*$B$7/100)/($B$8/10000*B25)</f>
         <v>1.143693958667472E-18</v>
       </c>
-      <c r="E23" s="22">
+      <c r="C23" s="19">
         <f>SQRT(
-(($D$10*D21*($E$7/100))/(($D$8/10000)*D25))^2
+(($B$10*B21*($C$7/100))/(($B$8/10000)*B25))^2
 +
-(($D$10*D21*($D$7/100)*($E$8/10000))/(($D$8/10000)^2*D25))^2
+(($B$10*B21*($B$7/100)*($C$8/10000))/(($B$8/10000)^2*B25))^2
 +
-(($D$10*D21*E25*($D$7/100))/(($D$8/10000)*D25^2))^2
+(($B$10*B21*C25*($B$7/100))/(($B$8/10000)*B25^2))^2
 )</f>
         <v>5.1122051938870741E-20</v>
       </c>
-      <c r="F23" s="21">
-        <f>(D10*$F$21*$D$7/100)/($D$8/10000*F25)</f>
+      <c r="D23" s="18">
+        <f>(B10*$D$21*$B$7/100)/($B$8/10000*D25)</f>
         <v>1.9889679113232534E-18</v>
       </c>
-      <c r="G23" s="22">
+      <c r="E23" s="19">
         <f>SQRT(
-(($D$10*F21*($E$7/100))/(($D$8/10000)*F25))^2
+(($B$10*D21*($C$7/100))/(($B$8/10000)*D25))^2
 +
-(($D$10*F21*($D$7/100)*($E$8/10000))/(($D$8/10000)^2*F25))^2
+(($B$10*D21*($B$7/100)*($C$8/10000))/(($B$8/10000)^2*D25))^2
 +
-(($D$10*F21*G25*($D$7/100))/(($D$8/10000)*F25^2))^2
+(($B$10*D21*E25*($B$7/100))/(($B$8/10000)*D25^2))^2
 )</f>
         <v>8.9121666461128602E-20</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>63</v>
-      </c>
-      <c r="C24" t="s">
-        <v>58</v>
-      </c>
-      <c r="D24" s="20">
+        <v>57</v>
+      </c>
+      <c r="B24" s="17">
+        <f>B23/B19</f>
+        <v>4.0313498719332813E-18</v>
+      </c>
+      <c r="C24" s="18">
+        <f>B23*C19/B19^2</f>
+        <v>5.6839617510515081E-21</v>
+      </c>
+      <c r="D24" s="18">
         <f>D23/D19</f>
-        <v>4.0313498719332813E-18</v>
-      </c>
-      <c r="E24" s="21">
+        <v>7.0108139278225357E-18</v>
+      </c>
+      <c r="E24" s="19">
         <f>D23*E19/D19^2</f>
-        <v>5.6839617510515081E-21</v>
-      </c>
-      <c r="F24" s="21">
-        <f>F23/F19</f>
-        <v>7.0108139278225357E-18</v>
-      </c>
-      <c r="G24" s="22">
-        <f>F23*G19/F19^2</f>
         <v>9.8848275330596208E-21</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C25" t="s">
-        <v>64</v>
-      </c>
-      <c r="D25" s="18">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>62</v>
+      </c>
+      <c r="B25" s="15">
+        <f>B22*100000</f>
+        <v>2411000</v>
+      </c>
+      <c r="C25" s="15">
+        <f>C22*100000</f>
+        <v>6027.5</v>
+      </c>
+      <c r="D25" s="15">
         <f>D22*100000</f>
-        <v>2411000</v>
-      </c>
-      <c r="E25" s="18">
+        <v>1368700</v>
+      </c>
+      <c r="E25" s="15">
         <f>E22*100000</f>
-        <v>6027.5</v>
-      </c>
-      <c r="F25" s="18">
-        <f>F22*100000</f>
-        <v>1368700</v>
-      </c>
-      <c r="G25" s="18">
-        <f>G22*100000</f>
         <v>5474.8</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A17:E17"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>